--- a/data_group/emmeans_intervalos_temp.xlsx
+++ b/data_group/emmeans_intervalos_temp.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">PF</t>
   </si>
   <si>
-    <t xml:space="preserve">TEMP</t>
+    <t xml:space="preserve">PREC</t>
   </si>
   <si>
     <t xml:space="preserve">1-10</t>
@@ -449,16 +449,16 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>26.0458158846612</v>
+        <v>26.0469073100349</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>25.8867193203397</v>
+        <v>26.0165991771096</v>
       </c>
       <c r="G2" t="n">
-        <v>26.2049124489826</v>
+        <v>26.0772154429602</v>
       </c>
     </row>
     <row r="3">
@@ -472,16 +472,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>25.8257692242717</v>
+        <v>25.8264542628721</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>25.6666726599505</v>
+        <v>25.8028168039263</v>
       </c>
       <c r="G3" t="n">
-        <v>25.9848657885929</v>
+        <v>25.8500917218178</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>25.687787517344</v>
+        <v>25.6880228169644</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>25.528690953023</v>
+        <v>25.6728689950933</v>
       </c>
       <c r="G4" t="n">
-        <v>25.8468840816649</v>
+        <v>25.7031766388355</v>
       </c>
     </row>
     <row r="5">
@@ -518,16 +518,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>25.6016919253991</v>
+        <v>25.6017031298139</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>25.4425953610784</v>
+        <v>25.5921136898375</v>
       </c>
       <c r="G5" t="n">
-        <v>25.7607884897198</v>
+        <v>25.6112925697903</v>
       </c>
     </row>
     <row r="6">
@@ -541,16 +541,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>25.5387112720047</v>
+        <v>25.5386854204973</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>25.379614707684</v>
+        <v>25.5335540055492</v>
       </c>
       <c r="G6" t="n">
-        <v>25.6978078363254</v>
+        <v>25.5438168354454</v>
       </c>
     </row>
     <row r="7">
@@ -564,16 +564,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>25.5091687622036</v>
+        <v>25.5092080361776</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>25.3500721978828</v>
+        <v>25.5061538847816</v>
       </c>
       <c r="G7" t="n">
-        <v>25.6682653265244</v>
+        <v>25.5122621875737</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>25.4420803765872</v>
+        <v>25.4420803770376</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>25.2829838122664</v>
+        <v>25.4420730242666</v>
       </c>
       <c r="G8" t="n">
-        <v>25.6011769409081</v>
+        <v>25.4420877298085</v>
       </c>
     </row>
     <row r="9">
@@ -610,16 +610,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>25.3753185662265</v>
+        <v>25.3753206788826</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>25.2162220019055</v>
+        <v>25.3731423483024</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5344151305476</v>
+        <v>25.3774990094628</v>
       </c>
     </row>
     <row r="10">
@@ -633,16 +633,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>25.3154123157704</v>
+        <v>25.3153841169128</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>25.1563157514494</v>
+        <v>25.3115543126219</v>
       </c>
       <c r="G10" t="n">
-        <v>25.4745088800914</v>
+        <v>25.3192139212038</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>24.9102935203089</v>
+        <v>24.9103563056581</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>24.7511969559885</v>
+        <v>24.896167848965</v>
       </c>
       <c r="G11" t="n">
-        <v>25.0693900846293</v>
+        <v>24.9245447623511</v>
       </c>
     </row>
     <row r="12">
@@ -679,16 +679,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>25.8849220382411</v>
+        <v>25.8806071230423</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>25.725825473914</v>
+        <v>25.842024778748</v>
       </c>
       <c r="G12" t="n">
-        <v>26.0440186025682</v>
+        <v>25.9191894673365</v>
       </c>
     </row>
     <row r="13">
@@ -702,16 +702,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>25.8248583682045</v>
+        <v>25.8183528156668</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>25.6657618038773</v>
+        <v>25.7723063985093</v>
       </c>
       <c r="G13" t="n">
-        <v>25.9839549325318</v>
+        <v>25.8643992328243</v>
       </c>
     </row>
     <row r="14">
@@ -725,16 +725,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>25.7890829467623</v>
+        <v>25.7854666261676</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>25.6299863824351</v>
+        <v>25.731997140293</v>
       </c>
       <c r="G14" t="n">
-        <v>25.9481795110895</v>
+        <v>25.8389361120422</v>
       </c>
     </row>
     <row r="15">
@@ -748,16 +748,16 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>25.6894984825401</v>
+        <v>25.6890978813705</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>25.5304019182128</v>
+        <v>25.6291610230566</v>
       </c>
       <c r="G15" t="n">
-        <v>25.8485950468674</v>
+        <v>25.7490347396844</v>
       </c>
     </row>
     <row r="16">
@@ -771,16 +771,16 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>25.6485258381895</v>
+        <v>25.6478216334423</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>25.4894292738622</v>
+        <v>25.5853677044927</v>
       </c>
       <c r="G16" t="n">
-        <v>25.8076224025168</v>
+        <v>25.7102755623919</v>
       </c>
     </row>
     <row r="17">
@@ -794,16 +794,16 @@
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>25.6664819944231</v>
+        <v>25.6688497781346</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>25.5073854300959</v>
+        <v>25.554408706202</v>
       </c>
       <c r="G17" t="n">
-        <v>25.8255785587503</v>
+        <v>25.7832908500671</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +817,16 @@
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>25.6369157657588</v>
+        <v>25.6483129049768</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>25.4778192014315</v>
+        <v>25.5558629924424</v>
       </c>
       <c r="G18" t="n">
-        <v>25.796012330086</v>
+        <v>25.7407628175111</v>
       </c>
     </row>
     <row r="19">
@@ -840,16 +840,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>25.6382070591541</v>
+        <v>25.6107181323977</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>25.4791104948268</v>
+        <v>25.481894529354</v>
       </c>
       <c r="G19" t="n">
-        <v>25.7973036234813</v>
+        <v>25.7395417354415</v>
       </c>
     </row>
     <row r="20">
@@ -863,16 +863,16 @@
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>25.33995338074</v>
+        <v>25.3356216895818</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>25.1798054934128</v>
+        <v>25.1949527691581</v>
       </c>
       <c r="G20" t="n">
-        <v>25.5001012680672</v>
+        <v>25.4762906100055</v>
       </c>
     </row>
     <row r="21">
@@ -886,16 +886,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>25.6081914133334</v>
+        <v>25.5314624062363</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>25.4451092877502</v>
+        <v>25.3898741779863</v>
       </c>
       <c r="G21" t="n">
-        <v>25.7712735389167</v>
+        <v>25.6730506344864</v>
       </c>
     </row>
     <row r="22">
@@ -909,16 +909,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>25.847198168866</v>
+        <v>25.8477178505201</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>25.688101604539</v>
+        <v>25.8179464774112</v>
       </c>
       <c r="G22" t="n">
-        <v>26.006294733193</v>
+        <v>25.8774892236289</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>25.8688923260461</v>
+        <v>25.871430503136</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>25.7097957617189</v>
+        <v>25.8363325724704</v>
       </c>
       <c r="G23" t="n">
-        <v>26.0279888903732</v>
+        <v>25.9065284338017</v>
       </c>
     </row>
     <row r="24">
@@ -955,16 +955,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>25.8400210257285</v>
+        <v>25.8460036839263</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>25.6809244614014</v>
+        <v>25.8068621529291</v>
       </c>
       <c r="G24" t="n">
-        <v>25.9991175900556</v>
+        <v>25.8851452149235</v>
       </c>
     </row>
     <row r="25">
@@ -978,16 +978,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>25.7879563582102</v>
+        <v>25.7997480657604</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
       </c>
       <c r="F25" t="n">
-        <v>25.628859793883</v>
+        <v>25.7551296778127</v>
       </c>
       <c r="G25" t="n">
-        <v>25.9470529225374</v>
+        <v>25.844366453708</v>
       </c>
     </row>
     <row r="26">
@@ -1001,16 +1001,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>25.7467739879847</v>
+        <v>25.7496870425416</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>25.5876774236575</v>
+        <v>25.703688065826</v>
       </c>
       <c r="G26" t="n">
-        <v>25.9058705523118</v>
+        <v>25.7956860192571</v>
       </c>
     </row>
     <row r="27">
@@ -1024,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>25.6707912997987</v>
+        <v>25.6757360383977</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>25.5116947354717</v>
+        <v>25.6310672661518</v>
       </c>
       <c r="G27" t="n">
-        <v>25.8298878641258</v>
+        <v>25.7204048106437</v>
       </c>
     </row>
     <row r="28">
@@ -1047,16 +1047,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>25.5965954367584</v>
+        <v>25.6112539121166</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>25.4374988724312</v>
+        <v>25.5642765305122</v>
       </c>
       <c r="G28" t="n">
-        <v>25.7556920010855</v>
+        <v>25.6582312937209</v>
       </c>
     </row>
     <row r="29">
@@ -1070,16 +1070,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>25.6453137864579</v>
+        <v>25.6384508443756</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>25.4862172221308</v>
+        <v>25.5774041750646</v>
       </c>
       <c r="G29" t="n">
-        <v>25.804410350785</v>
+        <v>25.6994975136867</v>
       </c>
     </row>
     <row r="30">
@@ -1093,16 +1093,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>25.5230432737404</v>
+        <v>25.4617237864691</v>
       </c>
       <c r="E30" t="s">
         <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>25.3639467094134</v>
+        <v>25.3947996516081</v>
       </c>
       <c r="G30" t="n">
-        <v>25.6821398380674</v>
+        <v>25.52864792133</v>
       </c>
     </row>
     <row r="31">
@@ -1116,16 +1116,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>25.4085253408478</v>
+        <v>25.3152982302995</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>25.2494287765207</v>
+        <v>25.1676977796729</v>
       </c>
       <c r="G31" t="n">
-        <v>25.5676219051749</v>
+        <v>25.462898680926</v>
       </c>
     </row>
     <row r="32">
@@ -1139,16 +1139,16 @@
         <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>25.878819885987</v>
+        <v>25.8530913114028</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>25.7147184672271</v>
+        <v>25.8165633022046</v>
       </c>
       <c r="G32" t="n">
-        <v>26.0429213047468</v>
+        <v>25.889619320601</v>
       </c>
     </row>
     <row r="33">
@@ -1162,16 +1162,16 @@
         <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>25.9404057871422</v>
+        <v>25.922339499777</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>25.7763043683823</v>
+        <v>25.8857213970472</v>
       </c>
       <c r="G33" t="n">
-        <v>26.1045072059022</v>
+        <v>25.9589576025068</v>
       </c>
     </row>
     <row r="34">
@@ -1185,16 +1185,16 @@
         <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>25.9203680688124</v>
+        <v>25.9101891735948</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>25.7562666500526</v>
+        <v>25.8691385329373</v>
       </c>
       <c r="G34" t="n">
-        <v>26.0844694875723</v>
+        <v>25.9512398142522</v>
       </c>
     </row>
     <row r="35">
@@ -1208,16 +1208,16 @@
         <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>25.8957080153011</v>
+        <v>25.8828011987853</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>25.731606596541</v>
+        <v>25.8350620904718</v>
       </c>
       <c r="G35" t="n">
-        <v>26.0598094340611</v>
+        <v>25.9305403070989</v>
       </c>
     </row>
     <row r="36">
@@ -1231,16 +1231,16 @@
         <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>25.8580683069251</v>
+        <v>25.8534855912485</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>25.6939668881652</v>
+        <v>25.8051732470767</v>
       </c>
       <c r="G36" t="n">
-        <v>26.0221697256851</v>
+        <v>25.9017979354203</v>
       </c>
     </row>
     <row r="37">
@@ -1254,16 +1254,16 @@
         <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>25.7673902414027</v>
+        <v>25.7650894686512</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>25.6032888226429</v>
+        <v>25.7125255395633</v>
       </c>
       <c r="G37" t="n">
-        <v>25.9314916601626</v>
+        <v>25.8176533977391</v>
       </c>
     </row>
     <row r="38">
@@ -1277,16 +1277,16 @@
         <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>25.7005855076344</v>
+        <v>25.6873702407074</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
       </c>
       <c r="F38" t="n">
-        <v>25.5364840888744</v>
+        <v>25.6428552289712</v>
       </c>
       <c r="G38" t="n">
-        <v>25.8646869263943</v>
+        <v>25.7318852524437</v>
       </c>
     </row>
     <row r="39">
@@ -1300,16 +1300,16 @@
         <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>25.6559011189694</v>
+        <v>25.6617503711059</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
       </c>
       <c r="F39" t="n">
-        <v>25.4917997002095</v>
+        <v>25.5940395383126</v>
       </c>
       <c r="G39" t="n">
-        <v>25.8200025377293</v>
+        <v>25.7294612038991</v>
       </c>
     </row>
     <row r="40">
@@ -1323,16 +1323,16 @@
         <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>25.5840344189285</v>
+        <v>25.5697793912851</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
       </c>
       <c r="F40" t="n">
-        <v>25.4199330001687</v>
+        <v>25.5117182434177</v>
       </c>
       <c r="G40" t="n">
-        <v>25.7481358376884</v>
+        <v>25.6278405391526</v>
       </c>
     </row>
     <row r="41">
@@ -1346,16 +1346,16 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>25.2991119854602</v>
+        <v>25.263583511867</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="n">
-        <v>25.1350105667003</v>
+        <v>25.2043935415709</v>
       </c>
       <c r="G41" t="n">
-        <v>25.4632134042201</v>
+        <v>25.3227734821631</v>
       </c>
     </row>
     <row r="42">
@@ -1369,16 +1369,16 @@
         <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>25.5475209067752</v>
+        <v>25.5484700515888</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>25.3976142570803</v>
+        <v>25.4854439292624</v>
       </c>
       <c r="G42" t="n">
-        <v>25.6974275564701</v>
+        <v>25.6114961739151</v>
       </c>
     </row>
     <row r="43">
@@ -1392,16 +1392,16 @@
         <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>25.3932856909706</v>
+        <v>25.3935918835044</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>25.243379041276</v>
+        <v>25.338077234332</v>
       </c>
       <c r="G43" t="n">
-        <v>25.5431923406652</v>
+        <v>25.4491065326767</v>
       </c>
     </row>
     <row r="44">
@@ -1415,16 +1415,16 @@
         <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>25.3260144215824</v>
+        <v>25.3254979386633</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>25.1761077718879</v>
+        <v>25.2755918008978</v>
       </c>
       <c r="G44" t="n">
-        <v>25.4759210712769</v>
+        <v>25.3754040764288</v>
       </c>
     </row>
     <row r="45">
@@ -1438,16 +1438,16 @@
         <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>25.3032882487166</v>
+        <v>25.3021480779094</v>
       </c>
       <c r="E45" t="s">
         <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>25.1533815990223</v>
+        <v>25.2606437620018</v>
       </c>
       <c r="G45" t="n">
-        <v>25.4531948984109</v>
+        <v>25.343652393817</v>
       </c>
     </row>
     <row r="46">
@@ -1461,16 +1461,16 @@
         <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>25.3472173432427</v>
+        <v>25.3463452332252</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>25.1973106935482</v>
+        <v>25.3115115596778</v>
       </c>
       <c r="G46" t="n">
-        <v>25.4971239929372</v>
+        <v>25.3811789067725</v>
       </c>
     </row>
     <row r="47">
@@ -1484,16 +1484,16 @@
         <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>25.3591294457079</v>
+        <v>25.3598378619062</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>25.2092227960134</v>
+        <v>25.3260374290775</v>
       </c>
       <c r="G47" t="n">
-        <v>25.5090360954024</v>
+        <v>25.393638294735</v>
       </c>
     </row>
     <row r="48">
@@ -1507,16 +1507,16 @@
         <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>25.2468379049576</v>
+        <v>25.2494981274987</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
       </c>
       <c r="F48" t="n">
-        <v>25.0969312552628</v>
+        <v>25.2127909307552</v>
       </c>
       <c r="G48" t="n">
-        <v>25.3967445546523</v>
+        <v>25.2862053242421</v>
       </c>
     </row>
     <row r="49">
@@ -1530,16 +1530,16 @@
         <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>25.1309643853327</v>
+        <v>25.1356359798866</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
       </c>
       <c r="F49" t="n">
-        <v>24.9810577356384</v>
+        <v>25.0961245998871</v>
       </c>
       <c r="G49" t="n">
-        <v>25.2808710350271</v>
+        <v>25.175147359886</v>
       </c>
     </row>
     <row r="50">
@@ -1553,16 +1553,16 @@
         <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>24.9950567614558</v>
+        <v>25.001458650452</v>
       </c>
       <c r="E50" t="s">
         <v>18</v>
       </c>
       <c r="F50" t="n">
-        <v>24.8451501117613</v>
+        <v>24.9581508168376</v>
       </c>
       <c r="G50" t="n">
-        <v>25.1449634111504</v>
+        <v>25.0447664840664</v>
       </c>
     </row>
     <row r="51">
@@ -1576,16 +1576,16 @@
         <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>24.5010569138636</v>
+        <v>24.5080709237316</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="n">
-        <v>24.3511502641684</v>
+        <v>24.4542429110494</v>
       </c>
       <c r="G51" t="n">
-        <v>24.6509635635588</v>
+        <v>24.5618989364139</v>
       </c>
     </row>
     <row r="52">
@@ -1599,16 +1599,16 @@
         <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>25.8588636400146</v>
+        <v>25.8560728830227</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="n">
-        <v>25.708956990322</v>
+        <v>25.8405852145825</v>
       </c>
       <c r="G52" t="n">
-        <v>26.0087702897072</v>
+        <v>25.8715605514629</v>
       </c>
     </row>
     <row r="53">
@@ -1622,16 +1622,16 @@
         <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>25.7692490013997</v>
+        <v>25.7685919804562</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="n">
-        <v>25.619342351707</v>
+        <v>25.7608893818151</v>
       </c>
       <c r="G53" t="n">
-        <v>25.9191556510925</v>
+        <v>25.7762945790974</v>
       </c>
     </row>
     <row r="54">
@@ -1645,16 +1645,16 @@
         <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>25.7254806969353</v>
+        <v>25.7236306540672</v>
       </c>
       <c r="E54" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="n">
-        <v>25.5755740472426</v>
+        <v>25.7074836165865</v>
       </c>
       <c r="G54" t="n">
-        <v>25.875387346628</v>
+        <v>25.739777691548</v>
       </c>
     </row>
     <row r="55">
@@ -1668,16 +1668,16 @@
         <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>25.6729195767872</v>
+        <v>25.6680187598825</v>
       </c>
       <c r="E55" t="s">
         <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>25.5230129270947</v>
+        <v>25.6457190898283</v>
       </c>
       <c r="G55" t="n">
-        <v>25.8228262264797</v>
+        <v>25.6903184299367</v>
       </c>
     </row>
     <row r="56">
@@ -1691,16 +1691,16 @@
         <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>25.615047861782</v>
+        <v>25.6061234765377</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>25.4651412120894</v>
+        <v>25.5824602463549</v>
       </c>
       <c r="G56" t="n">
-        <v>25.7649545114746</v>
+        <v>25.6297867067206</v>
       </c>
     </row>
     <row r="57">
@@ -1714,16 +1714,16 @@
         <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>25.5934838073841</v>
+        <v>25.5821778303766</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>25.4435771576916</v>
+        <v>25.552211921335</v>
       </c>
       <c r="G57" t="n">
-        <v>25.7433904570766</v>
+        <v>25.6121437394183</v>
       </c>
     </row>
     <row r="58">
@@ -1737,16 +1737,16 @@
         <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>25.528937059959</v>
+        <v>25.5189894215787</v>
       </c>
       <c r="E58" t="s">
         <v>16</v>
       </c>
       <c r="F58" t="n">
-        <v>25.3790304102665</v>
+        <v>25.489522300394</v>
       </c>
       <c r="G58" t="n">
-        <v>25.6788437096516</v>
+        <v>25.5484565427634</v>
       </c>
     </row>
     <row r="59">
@@ -1760,16 +1760,16 @@
         <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>25.4774074641507</v>
+        <v>25.4713837621266</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
       </c>
       <c r="F59" t="n">
-        <v>25.3275008144583</v>
+        <v>25.447358819484</v>
       </c>
       <c r="G59" t="n">
-        <v>25.6273141138432</v>
+        <v>25.4954087047693</v>
       </c>
     </row>
     <row r="60">
@@ -1783,16 +1783,16 @@
         <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>25.4071053268214</v>
+        <v>25.3946994676728</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="n">
-        <v>25.2571986771289</v>
+        <v>25.3623407431555</v>
       </c>
       <c r="G60" t="n">
-        <v>25.5570119765138</v>
+        <v>25.4270581921901</v>
       </c>
     </row>
     <row r="61">
@@ -1806,16 +1806,16 @@
         <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>25.3175164041701</v>
+        <v>25.3435142600504</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="n">
-        <v>25.1676097544777</v>
+        <v>25.29567583877</v>
       </c>
       <c r="G61" t="n">
-        <v>25.4674230538626</v>
+        <v>25.3913526813308</v>
       </c>
     </row>
     <row r="62">
@@ -1829,16 +1829,16 @@
         <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>25.8557396450652</v>
+        <v>25.8524812355983</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>25.7058329953726</v>
+        <v>25.8287670662411</v>
       </c>
       <c r="G62" t="n">
-        <v>26.0056462947578</v>
+        <v>25.8761954049556</v>
       </c>
     </row>
     <row r="63">
@@ -1852,16 +1852,16 @@
         <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>25.789924557819</v>
+        <v>25.7762202614944</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>25.6400179081262</v>
+        <v>25.7572568772019</v>
       </c>
       <c r="G63" t="n">
-        <v>25.9398312075118</v>
+        <v>25.795183645787</v>
       </c>
     </row>
     <row r="64">
@@ -1875,16 +1875,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>25.7376365950127</v>
+        <v>25.716781015446</v>
       </c>
       <c r="E64" t="s">
         <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>25.58772994532</v>
+        <v>25.6970388128405</v>
       </c>
       <c r="G64" t="n">
-        <v>25.8875432447054</v>
+        <v>25.7365232180515</v>
       </c>
     </row>
     <row r="65">
@@ -1898,16 +1898,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="n">
-        <v>25.6976990363773</v>
+        <v>25.6761676311224</v>
       </c>
       <c r="E65" t="s">
         <v>13</v>
       </c>
       <c r="F65" t="n">
-        <v>25.5477923866847</v>
+        <v>25.6560858271909</v>
       </c>
       <c r="G65" t="n">
-        <v>25.8476056860698</v>
+        <v>25.696249435054</v>
       </c>
     </row>
     <row r="66">
@@ -1921,16 +1921,16 @@
         <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>25.6541377792689</v>
+        <v>25.6344747910357</v>
       </c>
       <c r="E66" t="s">
         <v>14</v>
       </c>
       <c r="F66" t="n">
-        <v>25.5042311295763</v>
+        <v>25.6142188000324</v>
       </c>
       <c r="G66" t="n">
-        <v>25.8040444289615</v>
+        <v>25.6547307820389</v>
       </c>
     </row>
     <row r="67">
@@ -1944,16 +1944,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>25.615824000115</v>
+        <v>25.5917153562024</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>25.4659173504225</v>
+        <v>25.5678124191535</v>
       </c>
       <c r="G67" t="n">
-        <v>25.7657306498075</v>
+        <v>25.6156182932512</v>
       </c>
     </row>
     <row r="68">
@@ -1967,16 +1967,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>25.5471115440873</v>
+        <v>25.5276734070192</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>25.3972048943947</v>
+        <v>25.5019957240599</v>
       </c>
       <c r="G68" t="n">
-        <v>25.6970181937799</v>
+        <v>25.5533510899785</v>
       </c>
     </row>
     <row r="69">
@@ -1990,16 +1990,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>25.4902823730133</v>
+        <v>25.4703117284536</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
       </c>
       <c r="F69" t="n">
-        <v>25.3403757233208</v>
+        <v>25.442307447981</v>
       </c>
       <c r="G69" t="n">
-        <v>25.6401890227058</v>
+        <v>25.4983160089262</v>
       </c>
     </row>
     <row r="70">
@@ -2013,16 +2013,16 @@
         <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>25.3688236916028</v>
+        <v>25.3467116298182</v>
       </c>
       <c r="E70" t="s">
         <v>18</v>
       </c>
       <c r="F70" t="n">
-        <v>25.2189170419103</v>
+        <v>25.3170129577225</v>
       </c>
       <c r="G70" t="n">
-        <v>25.5187303412953</v>
+        <v>25.3764103019138</v>
       </c>
     </row>
     <row r="71">
@@ -2036,16 +2036,16 @@
         <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>25.2613302942671</v>
+        <v>25.2348650201871</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>25.1114236445747</v>
+        <v>25.2003349567853</v>
       </c>
       <c r="G71" t="n">
-        <v>25.4112369439596</v>
+        <v>25.2693950835889</v>
       </c>
     </row>
     <row r="72">
@@ -2059,16 +2059,16 @@
         <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>25.8866360238909</v>
+        <v>25.869427342237</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>25.7352301814158</v>
+        <v>25.844381615991</v>
       </c>
       <c r="G72" t="n">
-        <v>26.038041866366</v>
+        <v>25.8944730684831</v>
       </c>
     </row>
     <row r="73">
@@ -2082,16 +2082,16 @@
         <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>25.7961079631741</v>
+        <v>25.7859258260335</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="F73" t="n">
-        <v>25.6447021206989</v>
+        <v>25.7711910214292</v>
       </c>
       <c r="G73" t="n">
-        <v>25.9475138056494</v>
+        <v>25.8006606306378</v>
       </c>
     </row>
     <row r="74">
@@ -2105,16 +2105,16 @@
         <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>25.7022961927397</v>
+        <v>25.6962308557908</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
       </c>
       <c r="F74" t="n">
-        <v>25.5508903502646</v>
+        <v>25.6852227009794</v>
       </c>
       <c r="G74" t="n">
-        <v>25.8537020352149</v>
+        <v>25.7072390106021</v>
       </c>
     </row>
     <row r="75">
@@ -2128,16 +2128,16 @@
         <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>25.6573412573726</v>
+        <v>25.6511550708072</v>
       </c>
       <c r="E75" t="s">
         <v>13</v>
       </c>
       <c r="F75" t="n">
-        <v>25.5059354148977</v>
+        <v>25.6406689633672</v>
       </c>
       <c r="G75" t="n">
-        <v>25.8087470998476</v>
+        <v>25.6616411782473</v>
       </c>
     </row>
     <row r="76">
@@ -2151,16 +2151,16 @@
         <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>25.6194295767751</v>
+        <v>25.6033637200628</v>
       </c>
       <c r="E76" t="s">
         <v>14</v>
       </c>
       <c r="F76" t="n">
-        <v>25.4680237343</v>
+        <v>25.592813551162</v>
       </c>
       <c r="G76" t="n">
-        <v>25.7708354192501</v>
+        <v>25.6139138889637</v>
       </c>
     </row>
     <row r="77">
@@ -2174,16 +2174,16 @@
         <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>25.5901537634747</v>
+        <v>25.5747905227714</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>25.4387479209998</v>
+        <v>25.5611268553598</v>
       </c>
       <c r="G77" t="n">
-        <v>25.7415596059497</v>
+        <v>25.5884541901831</v>
       </c>
     </row>
     <row r="78">
@@ -2197,16 +2197,16 @@
         <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>25.5278355465639</v>
+        <v>25.5134788862612</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
       </c>
       <c r="F78" t="n">
-        <v>25.3764297040888</v>
+        <v>25.4989538691015</v>
       </c>
       <c r="G78" t="n">
-        <v>25.6792413890389</v>
+        <v>25.5280039034208</v>
       </c>
     </row>
     <row r="79">
@@ -2220,16 +2220,16 @@
         <v>9</v>
       </c>
       <c r="D79" t="n">
-        <v>25.4468528589829</v>
+        <v>25.4347018454818</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
       </c>
       <c r="F79" t="n">
-        <v>25.2954470165079</v>
+        <v>25.4185069257414</v>
       </c>
       <c r="G79" t="n">
-        <v>25.5982587014579</v>
+        <v>25.4508967652222</v>
       </c>
     </row>
     <row r="80">
@@ -2243,16 +2243,16 @@
         <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>25.3344607139283</v>
+        <v>25.3221474926086</v>
       </c>
       <c r="E80" t="s">
         <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>25.1830548714533</v>
+        <v>25.3032039450696</v>
       </c>
       <c r="G80" t="n">
-        <v>25.4858665564032</v>
+        <v>25.3410910401477</v>
       </c>
     </row>
     <row r="81">
@@ -2266,16 +2266,16 @@
         <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>25.1690251054195</v>
+        <v>25.1711775587113</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="n">
-        <v>25.0176192629446</v>
+        <v>25.1484256431561</v>
       </c>
       <c r="G81" t="n">
-        <v>25.3204309478945</v>
+        <v>25.1939294742664</v>
       </c>
     </row>
     <row r="82">
@@ -2289,16 +2289,16 @@
         <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>25.2666616138707</v>
+        <v>25.2695134640719</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>25.0947300144698</v>
+        <v>25.2459479508002</v>
       </c>
       <c r="G82" t="n">
-        <v>25.4385932132716</v>
+        <v>25.2930789773437</v>
       </c>
     </row>
     <row r="83">
@@ -2312,16 +2312,16 @@
         <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>25.1888473858282</v>
+        <v>25.1904139692511</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="F83" t="n">
-        <v>25.0169157864286</v>
+        <v>25.1715697502923</v>
       </c>
       <c r="G83" t="n">
-        <v>25.3607789852278</v>
+        <v>25.2092581882098</v>
       </c>
     </row>
     <row r="84">
@@ -2335,16 +2335,16 @@
         <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>25.1220395728907</v>
+        <v>25.1224071065132</v>
       </c>
       <c r="E84" t="s">
         <v>12</v>
       </c>
       <c r="F84" t="n">
-        <v>24.9501079734914</v>
+        <v>25.1107965863931</v>
       </c>
       <c r="G84" t="n">
-        <v>25.2939711722901</v>
+        <v>25.1340176266333</v>
       </c>
     </row>
     <row r="85">
@@ -2358,16 +2358,16 @@
         <v>9</v>
       </c>
       <c r="D85" t="n">
-        <v>25.0865904666814</v>
+        <v>25.0866382918527</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
       </c>
       <c r="F85" t="n">
-        <v>24.9146588672818</v>
+        <v>25.0784732281398</v>
       </c>
       <c r="G85" t="n">
-        <v>25.2585220660811</v>
+        <v>25.0948033555655</v>
       </c>
     </row>
     <row r="86">
@@ -2381,16 +2381,16 @@
         <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>25.1876041122628</v>
+        <v>25.1888436819644</v>
       </c>
       <c r="E86" t="s">
         <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>25.0156725128629</v>
+        <v>25.1796924628473</v>
       </c>
       <c r="G86" t="n">
-        <v>25.3595357116627</v>
+        <v>25.1979949010815</v>
       </c>
     </row>
     <row r="87">
@@ -2404,16 +2404,16 @@
         <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>25.2855496288246</v>
+        <v>25.2857339590974</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>25.1136180294242</v>
+        <v>25.2796070103359</v>
       </c>
       <c r="G87" t="n">
-        <v>25.457481228225</v>
+        <v>25.2918609078589</v>
       </c>
     </row>
     <row r="88">
@@ -2427,16 +2427,16 @@
         <v>9</v>
       </c>
       <c r="D88" t="n">
-        <v>25.16945815293</v>
+        <v>25.16956287215</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
       </c>
       <c r="F88" t="n">
-        <v>24.9975265535296</v>
+        <v>25.1638444438111</v>
       </c>
       <c r="G88" t="n">
-        <v>25.3413897523303</v>
+        <v>25.175281300489</v>
       </c>
     </row>
     <row r="89">
@@ -2450,16 +2450,16 @@
         <v>9</v>
       </c>
       <c r="D89" t="n">
-        <v>25.0597774471671</v>
+        <v>25.0601275882654</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
       </c>
       <c r="F89" t="n">
-        <v>24.8878458477672</v>
+        <v>25.0517180627234</v>
       </c>
       <c r="G89" t="n">
-        <v>25.2317090465669</v>
+        <v>25.0685371138075</v>
       </c>
     </row>
     <row r="90">
@@ -2473,16 +2473,16 @@
         <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>24.9496740397818</v>
+        <v>24.9505375691259</v>
       </c>
       <c r="E90" t="s">
         <v>18</v>
       </c>
       <c r="F90" t="n">
-        <v>24.7777424403823</v>
+        <v>24.9381678576915</v>
       </c>
       <c r="G90" t="n">
-        <v>25.1216056391813</v>
+        <v>24.9629072805602</v>
       </c>
     </row>
     <row r="91">
@@ -2496,16 +2496,16 @@
         <v>9</v>
       </c>
       <c r="D91" t="n">
-        <v>24.5873165307819</v>
+        <v>24.5902344877997</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="n">
-        <v>24.4153849313828</v>
+        <v>24.5601973217874</v>
       </c>
       <c r="G91" t="n">
-        <v>24.7592481301811</v>
+        <v>24.620271653812</v>
       </c>
     </row>
     <row r="92">
@@ -2519,16 +2519,16 @@
         <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>25.8546238434838</v>
+        <v>25.8644534097431</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>25.6826922440894</v>
+        <v>25.8262652557719</v>
       </c>
       <c r="G92" t="n">
-        <v>26.0265554428782</v>
+        <v>25.9026415637142</v>
       </c>
     </row>
     <row r="93">
@@ -2542,16 +2542,16 @@
         <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>25.6415639103494</v>
+        <v>25.6529155846636</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>25.4696323109551</v>
+        <v>25.6256093436861</v>
       </c>
       <c r="G93" t="n">
-        <v>25.8134955097437</v>
+        <v>25.6802218256411</v>
       </c>
     </row>
     <row r="94">
@@ -2565,16 +2565,16 @@
         <v>9</v>
       </c>
       <c r="D94" t="n">
-        <v>25.4658267477683</v>
+        <v>25.4665403550656</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>25.2938951483738</v>
+        <v>25.4418619346876</v>
       </c>
       <c r="G94" t="n">
-        <v>25.6377583471628</v>
+        <v>25.4912187754435</v>
       </c>
     </row>
     <row r="95">
@@ -2588,16 +2588,16 @@
         <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>25.3145522691824</v>
+        <v>25.3051497385154</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>25.1426206697877</v>
+        <v>25.2768455282612</v>
       </c>
       <c r="G95" t="n">
-        <v>25.4864838685771</v>
+        <v>25.3334539487697</v>
       </c>
     </row>
     <row r="96">
@@ -2611,16 +2611,16 @@
         <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>25.225638782726</v>
+        <v>25.2188730692113</v>
       </c>
       <c r="E96" t="s">
         <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>25.0537071833315</v>
+        <v>25.1922341687488</v>
       </c>
       <c r="G96" t="n">
-        <v>25.3975703821205</v>
+        <v>25.2455119696738</v>
       </c>
     </row>
     <row r="97">
@@ -2634,16 +2634,16 @@
         <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>25.1139831340761</v>
+        <v>25.0809846473651</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>24.9420515346816</v>
+        <v>25.0470072700809</v>
       </c>
       <c r="G97" t="n">
-        <v>25.2859147334706</v>
+        <v>25.1149620246493</v>
       </c>
     </row>
     <row r="98">
@@ -2657,16 +2657,16 @@
         <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>25.0391313463755</v>
+        <v>24.9826341852972</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>24.8671997469808</v>
+        <v>24.9363145167078</v>
       </c>
       <c r="G98" t="n">
-        <v>25.2110629457703</v>
+        <v>25.0289538538866</v>
       </c>
     </row>
     <row r="99">
@@ -2680,16 +2680,16 @@
         <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>24.8925513212202</v>
+        <v>24.838453804175</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
       </c>
       <c r="F99" t="n">
-        <v>24.7206197218258</v>
+        <v>24.7927677546532</v>
       </c>
       <c r="G99" t="n">
-        <v>25.0644829206146</v>
+        <v>24.8841398536969</v>
       </c>
     </row>
     <row r="100">
@@ -2703,16 +2703,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>24.8128489755132</v>
+        <v>24.7958303041163</v>
       </c>
       <c r="E100" t="s">
         <v>18</v>
       </c>
       <c r="F100" t="n">
-        <v>24.6409173761187</v>
+        <v>24.7497182828446</v>
       </c>
       <c r="G100" t="n">
-        <v>24.9847805749076</v>
+        <v>24.8419423253881</v>
       </c>
     </row>
     <row r="101">
@@ -2726,16 +2726,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>24.6565395452306</v>
+        <v>24.5443322348006</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
       </c>
       <c r="F101" t="n">
-        <v>24.4846079458362</v>
+        <v>24.4647278277895</v>
       </c>
       <c r="G101" t="n">
-        <v>24.828471144625</v>
+        <v>24.6239366418117</v>
       </c>
     </row>
     <row r="102">
@@ -2749,16 +2749,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>25.8122505515455</v>
+        <v>25.8565845659503</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
       </c>
       <c r="F102" t="n">
-        <v>25.6403189521511</v>
+        <v>25.80511950497</v>
       </c>
       <c r="G102" t="n">
-        <v>25.9841821509399</v>
+        <v>25.9080496269307</v>
       </c>
     </row>
     <row r="103">
@@ -2772,16 +2772,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>25.7224960134234</v>
+        <v>25.7611256246855</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>25.5505644140291</v>
+        <v>25.708629260761</v>
       </c>
       <c r="G103" t="n">
-        <v>25.8944276128178</v>
+        <v>25.81362198861</v>
       </c>
     </row>
     <row r="104">
@@ -2795,16 +2795,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>25.6267018319839</v>
+        <v>25.6564388612986</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>25.4547702325895</v>
+        <v>25.602657640396</v>
       </c>
       <c r="G104" t="n">
-        <v>25.7986334313784</v>
+        <v>25.7102200822012</v>
       </c>
     </row>
     <row r="105">
@@ -2818,16 +2818,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="n">
-        <v>25.5023091684757</v>
+        <v>25.516589590925</v>
       </c>
       <c r="E105" t="s">
         <v>13</v>
       </c>
       <c r="F105" t="n">
-        <v>25.330377569081</v>
+        <v>25.4675169103274</v>
       </c>
       <c r="G105" t="n">
-        <v>25.6742407678704</v>
+        <v>25.5656622715226</v>
       </c>
     </row>
     <row r="106">
@@ -2841,16 +2841,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>25.3913651086338</v>
+        <v>25.3978989543721</v>
       </c>
       <c r="E106" t="s">
         <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>25.2194335092393</v>
+        <v>25.3620084231861</v>
       </c>
       <c r="G106" t="n">
-        <v>25.5632967080284</v>
+        <v>25.4337894855582</v>
       </c>
     </row>
     <row r="107">
@@ -2864,16 +2864,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>25.3405917173887</v>
+        <v>25.3290867758411</v>
       </c>
       <c r="E107" t="s">
         <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>25.1686601179941</v>
+        <v>25.2901177771477</v>
       </c>
       <c r="G107" t="n">
-        <v>25.5125233167832</v>
+        <v>25.3680557745345</v>
       </c>
     </row>
     <row r="108">
@@ -2887,16 +2887,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>25.2175540697929</v>
+        <v>25.213071187149</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="n">
-        <v>25.0456224703982</v>
+        <v>25.162338066402</v>
       </c>
       <c r="G108" t="n">
-        <v>25.3894856691876</v>
+        <v>25.263804307896</v>
       </c>
     </row>
     <row r="109">
@@ -2910,16 +2910,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>25.0877763991161</v>
+        <v>25.0729354620705</v>
       </c>
       <c r="E109" t="s">
         <v>17</v>
       </c>
       <c r="F109" t="n">
-        <v>24.9158447997217</v>
+        <v>25.0233508612641</v>
       </c>
       <c r="G109" t="n">
-        <v>25.2597079985105</v>
+        <v>25.122520062877</v>
       </c>
     </row>
     <row r="110">
@@ -2933,16 +2933,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>24.9482248347157</v>
+        <v>24.9549066130395</v>
       </c>
       <c r="E110" t="s">
         <v>18</v>
       </c>
       <c r="F110" t="n">
-        <v>24.7762932353212</v>
+        <v>24.9227696953238</v>
       </c>
       <c r="G110" t="n">
-        <v>25.1201564341101</v>
+        <v>24.9870435307553</v>
       </c>
     </row>
     <row r="111">
@@ -2956,16 +2956,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>24.7900194549429</v>
+        <v>24.7718578110971</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
       <c r="F111" t="n">
-        <v>24.6180878555484</v>
+        <v>24.7407751349691</v>
       </c>
       <c r="G111" t="n">
-        <v>24.9619510543373</v>
+        <v>24.8029404872252</v>
       </c>
     </row>
     <row r="112">
@@ -2979,16 +2979,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>25.7741657132707</v>
+        <v>25.8011782437645</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>25.6001474613773</v>
+        <v>25.7580472603698</v>
       </c>
       <c r="G112" t="n">
-        <v>25.9481839651641</v>
+        <v>25.8443092271591</v>
       </c>
     </row>
     <row r="113">
@@ -3002,16 +3002,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="n">
-        <v>25.7222825272642</v>
+        <v>25.7586578127168</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="F113" t="n">
-        <v>25.5482642753708</v>
+        <v>25.7136744734997</v>
       </c>
       <c r="G113" t="n">
-        <v>25.8963007791576</v>
+        <v>25.803641151934</v>
       </c>
     </row>
     <row r="114">
@@ -3025,16 +3025,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>25.6071877906521</v>
+        <v>25.6479359504949</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
       </c>
       <c r="F114" t="n">
-        <v>25.4331695387586</v>
+        <v>25.6058802857183</v>
       </c>
       <c r="G114" t="n">
-        <v>25.7812060425457</v>
+        <v>25.6899916152716</v>
       </c>
     </row>
     <row r="115">
@@ -3048,16 +3048,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>25.5182643300475</v>
+        <v>25.5568546294306</v>
       </c>
       <c r="E115" t="s">
         <v>13</v>
       </c>
       <c r="F115" t="n">
-        <v>25.3442460781537</v>
+        <v>25.5148215160707</v>
       </c>
       <c r="G115" t="n">
-        <v>25.6922825819412</v>
+        <v>25.5988877427906</v>
       </c>
     </row>
     <row r="116">
@@ -3071,16 +3071,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>25.4174390374064</v>
+        <v>25.4640183725181</v>
       </c>
       <c r="E116" t="s">
         <v>14</v>
       </c>
       <c r="F116" t="n">
-        <v>25.2434207855129</v>
+        <v>25.4135542843997</v>
       </c>
       <c r="G116" t="n">
-        <v>25.5914572893</v>
+        <v>25.5144824606364</v>
       </c>
     </row>
     <row r="117">
@@ -3094,16 +3094,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>25.345256603849</v>
+        <v>25.3826956986025</v>
       </c>
       <c r="E117" t="s">
         <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>25.1712383519554</v>
+        <v>25.3367841131847</v>
       </c>
       <c r="G117" t="n">
-        <v>25.5192748557425</v>
+        <v>25.4286072840203</v>
       </c>
     </row>
     <row r="118">
@@ -3117,16 +3117,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="n">
-        <v>25.2405148616061</v>
+        <v>25.3043130157942</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
       </c>
       <c r="F118" t="n">
-        <v>25.0664966097123</v>
+        <v>25.2329185689726</v>
       </c>
       <c r="G118" t="n">
-        <v>25.4145331134998</v>
+        <v>25.3757074626159</v>
       </c>
     </row>
     <row r="119">
@@ -3140,16 +3140,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>24.9372316622198</v>
+        <v>24.9678289330953</v>
       </c>
       <c r="E119" t="s">
         <v>17</v>
       </c>
       <c r="F119" t="n">
-        <v>24.7632134103263</v>
+        <v>24.9222853858667</v>
       </c>
       <c r="G119" t="n">
-        <v>25.1112499141132</v>
+        <v>25.013372480324</v>
       </c>
     </row>
     <row r="120">
@@ -3163,16 +3163,16 @@
         <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>24.9227782555969</v>
+        <v>24.9391371398269</v>
       </c>
       <c r="E120" t="s">
         <v>18</v>
       </c>
       <c r="F120" t="n">
-        <v>24.7487600037033</v>
+        <v>24.8917437705413</v>
       </c>
       <c r="G120" t="n">
-        <v>25.0967965074904</v>
+        <v>24.9865305091124</v>
       </c>
     </row>
     <row r="121">
@@ -3186,16 +3186,16 @@
         <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>24.6274810218104</v>
+        <v>24.632734018645</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
       </c>
       <c r="F121" t="n">
-        <v>24.453462769917</v>
+        <v>24.5960700441803</v>
       </c>
       <c r="G121" t="n">
-        <v>24.8014992737039</v>
+        <v>24.6693979931097</v>
       </c>
     </row>
   </sheetData>
